--- a/output/2026-09-09_四大力量牛熊週期_日內交易框架.xlsx
+++ b/output/2026-09-09_四大力量牛熊週期_日內交易框架.xlsx
@@ -15,6 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_領先指標儀表板" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_日內交易劇本" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_資料來源" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TV_連結" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,7 +27,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -97,6 +98,15 @@
     <font>
       <i val="1"/>
       <color rgb="00808080"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <color rgb="00595959"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -208,7 +218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -312,6 +322,60 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -390,7 +454,6 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -488,7 +551,6 @@
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="12"/>
   <chart>
     <title>
       <tx>
@@ -607,7 +669,6 @@
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="11"/>
   <chart>
     <title>
       <tx>
@@ -744,7 +805,6 @@
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="12"/>
   <chart>
     <title>
       <tx>
@@ -845,7 +905,6 @@
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="13"/>
   <chart>
     <title>
       <tx>
@@ -1391,6 +1450,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1587,6 +1647,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
@@ -1691,6 +1752,8 @@
       <c r="F16" s="10" t="n"/>
       <c r="G16" s="11" t="n"/>
     </row>
+    <row r="17"/>
+    <row r="18"/>
     <row r="19" hidden="1">
       <c r="A19" t="inlineStr">
         <is>
@@ -1792,6 +1855,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2482,6 +2546,8 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
+    <row r="24"/>
     <row r="25" hidden="1">
       <c r="A25" t="inlineStr">
         <is>
@@ -2698,6 +2764,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -3258,6 +3325,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="20" t="inlineStr">
         <is>
@@ -3387,6 +3455,28 @@
       <c r="F29" s="10" t="n"/>
       <c r="G29" s="11" t="n"/>
     </row>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
     <row r="52" ht="24" customHeight="1">
       <c r="A52" s="20" t="inlineStr">
         <is>
@@ -3454,6 +3544,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -3706,6 +3797,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="20" t="inlineStr">
         <is>
@@ -3816,6 +3908,27 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
     <row r="41" ht="24" customHeight="1">
       <c r="A41" s="20" t="inlineStr">
         <is>
@@ -3920,7 +4033,7 @@
       </c>
       <c r="C46" s="10" t="n"/>
       <c r="D46" s="11" t="n"/>
-      <c r="E46" s="4" t="inlineStr">
+      <c r="E46" s="41" t="inlineStr">
         <is>
           <t>未出現：NVDA 4.3 萬億美元仍在高位</t>
         </is>
@@ -3970,6 +4083,7 @@
       <c r="F48" s="10" t="n"/>
       <c r="G48" s="11" t="n"/>
     </row>
+    <row r="49"/>
     <row r="50" ht="24" customHeight="1">
       <c r="A50" s="20" t="inlineStr">
         <is>
@@ -4007,8 +4121,11 @@
     <mergeCell ref="B47:D47"/>
     <mergeCell ref="B48:D48"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -4044,6 +4161,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -4359,6 +4477,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="20" t="inlineStr">
         <is>
@@ -4534,6 +4653,26 @@
       <c r="F22" s="10" t="n"/>
       <c r="G22" s="11" t="n"/>
     </row>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
     <row r="43" ht="24" customHeight="1">
       <c r="A43" s="20" t="inlineStr">
         <is>
@@ -4610,6 +4749,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -4643,7 +4783,7 @@
       </c>
     </row>
     <row r="5" ht="42" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="41" t="inlineStr">
         <is>
           <t>Brent 原油</t>
         </is>
@@ -4675,7 +4815,7 @@
       </c>
     </row>
     <row r="6" ht="42" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="42" t="inlineStr">
         <is>
           <t>Brent 按年變動</t>
         </is>
@@ -4771,7 +4911,7 @@
       </c>
     </row>
     <row r="9" ht="42" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="41" t="inlineStr">
         <is>
           <t>10 年期美債孳息</t>
         </is>
@@ -4803,7 +4943,7 @@
       </c>
     </row>
     <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="42" t="inlineStr">
         <is>
           <t>VIX</t>
         </is>
@@ -4835,7 +4975,7 @@
       </c>
     </row>
     <row r="11" ht="42" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="41" t="inlineStr">
         <is>
           <t>標普 500</t>
         </is>
@@ -4867,7 +5007,7 @@
       </c>
     </row>
     <row r="12" ht="42" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="42" t="inlineStr">
         <is>
           <t>黃金</t>
         </is>
@@ -4899,7 +5039,7 @@
       </c>
     </row>
     <row r="13" ht="42" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="41" t="inlineStr">
         <is>
           <t>Brent 期貨曲線形態</t>
         </is>
@@ -5026,6 +5166,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="20" t="inlineStr">
         <is>
@@ -5048,6 +5189,15 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A18:F18"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5083,6 +5233,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="20" t="inlineStr">
         <is>
@@ -5370,6 +5521,7 @@
       </c>
       <c r="F14" s="27" t="n"/>
     </row>
+    <row r="15"/>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="20" t="inlineStr">
         <is>
@@ -5629,6 +5781,7 @@
       </c>
       <c r="F25" s="36" t="n"/>
     </row>
+    <row r="26"/>
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="20" t="inlineStr">
         <is>
@@ -5888,6 +6041,7 @@
       </c>
       <c r="F36" s="27" t="n"/>
     </row>
+    <row r="37"/>
     <row r="38" ht="24" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
         <is>
@@ -5925,7 +6079,7 @@
           <t>偏多</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B40" s="41" t="inlineStr">
         <is>
           <t>能源 (XLE)、油服、油輪航運</t>
         </is>
@@ -5997,7 +6151,7 @@
           <t>偏多</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B43" s="41" t="inlineStr">
         <is>
           <t>波動率 (VIX 買權 / 尾部保護)</t>
         </is>
@@ -6087,6 +6241,7 @@
       <c r="E46" s="27" t="n"/>
       <c r="F46" s="27" t="n"/>
     </row>
+    <row r="47"/>
     <row r="48" ht="24" customHeight="1">
       <c r="A48" s="20" t="inlineStr">
         <is>
@@ -6178,6 +6333,7 @@
       <c r="E55" s="10" t="n"/>
       <c r="F55" s="11" t="n"/>
     </row>
+    <row r="56"/>
     <row r="57" ht="40" customHeight="1">
       <c r="A57" s="40" t="inlineStr">
         <is>
@@ -6203,6 +6359,10 @@
     <mergeCell ref="A55:F55"/>
     <mergeCell ref="A57:F57"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B40" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B43" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6228,6 +6388,8 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -6331,7 +6493,7 @@
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="42" t="inlineStr">
         <is>
           <t>10 年期孳息 / VIX / 黃金</t>
         </is>
@@ -6436,6 +6598,232 @@
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>TradingView 連結索引（本檔案出現過的所有代號）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="43" t="inlineStr">
+        <is>
+          <t>原地已加連結的儲存格：0 個。另有 0 個儲存格同時提及多個代號 —— Excel 不支援在單一儲存格內為部分文字加連結，故該類儲存格不在原地處理，改由本表覆蓋。點擊下方連結即可開啟該代號的 TradingView 圖表。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="44" t="inlineStr">
+        <is>
+          <t>代號</t>
+        </is>
+      </c>
+      <c r="B4" s="44" t="inlineStr">
+        <is>
+          <t>名稱</t>
+        </is>
+      </c>
+      <c r="C4" s="44" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="D4" s="44" t="inlineStr">
+        <is>
+          <t>出現位置</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="53" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B5" s="54" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C5" s="55" t="inlineStr">
+        <is>
+          <t>NASDAQ:NVDA</t>
+        </is>
+      </c>
+      <c r="D5" s="48" t="inlineStr">
+        <is>
+          <t>03_技術革命週期!E46</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="56" t="inlineStr">
+        <is>
+          <t>VIX</t>
+        </is>
+      </c>
+      <c r="B6" s="57" t="inlineStr">
+        <is>
+          <t>CBOE 波動率指數</t>
+        </is>
+      </c>
+      <c r="C6" s="58" t="inlineStr">
+        <is>
+          <t>CBOE:VIX</t>
+        </is>
+      </c>
+      <c r="D6" s="52" t="inlineStr">
+        <is>
+          <t>00_現況定位!B13、00_現況定位!B16、04_黑天鵝地緣週期!E22、05_領先指標儀表板!A10、05_領先指標儀表板!A19、06_日內交易劇本!B43 …等 9 處</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="53" t="inlineStr">
+        <is>
+          <t>XLE</t>
+        </is>
+      </c>
+      <c r="B7" s="54" t="inlineStr">
+        <is>
+          <t>能源類股 ETF</t>
+        </is>
+      </c>
+      <c r="C7" s="55" t="inlineStr">
+        <is>
+          <t>AMEX:XLE</t>
+        </is>
+      </c>
+      <c r="D7" s="48" t="inlineStr">
+        <is>
+          <t>06_日內交易劇本!E30、06_日內交易劇本!B40</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="56" t="inlineStr">
+        <is>
+          <t>GOLD</t>
+        </is>
+      </c>
+      <c r="B8" s="57" t="inlineStr">
+        <is>
+          <t>黃金現貨</t>
+        </is>
+      </c>
+      <c r="C8" s="58" t="inlineStr">
+        <is>
+          <t>TVC:GOLD</t>
+        </is>
+      </c>
+      <c r="D8" s="52" t="inlineStr">
+        <is>
+          <t>05_領先指標儀表板!A12</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="53" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="B9" s="54" t="inlineStr">
+        <is>
+          <t>標普 500 指數</t>
+        </is>
+      </c>
+      <c r="C9" s="55" t="inlineStr">
+        <is>
+          <t>SP:SPX</t>
+        </is>
+      </c>
+      <c r="D9" s="48" t="inlineStr">
+        <is>
+          <t>05_領先指標儀表板!A11</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="56" t="inlineStr">
+        <is>
+          <t>UKOIL</t>
+        </is>
+      </c>
+      <c r="B10" s="57" t="inlineStr">
+        <is>
+          <t>Brent 原油</t>
+        </is>
+      </c>
+      <c r="C10" s="58" t="inlineStr">
+        <is>
+          <t>TVC:UKOIL</t>
+        </is>
+      </c>
+      <c r="D10" s="52" t="inlineStr">
+        <is>
+          <t>05_領先指標儀表板!A5、05_領先指標儀表板!A6、05_領先指標儀表板!A13</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="53" t="inlineStr">
+        <is>
+          <t>US10Y</t>
+        </is>
+      </c>
+      <c r="B11" s="54" t="inlineStr">
+        <is>
+          <t>美國 10 年期孳息</t>
+        </is>
+      </c>
+      <c r="C11" s="55" t="inlineStr">
+        <is>
+          <t>TVC:US10Y</t>
+        </is>
+      </c>
+      <c r="D11" s="48" t="inlineStr">
+        <is>
+          <t>05_領先指標儀表板!A9</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/2026-09-09_四大力量牛熊週期_日內交易框架.xlsx
+++ b/output/2026-09-09_四大力量牛熊週期_日內交易框架.xlsx
@@ -218,7 +218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -357,6 +357,24 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -6657,17 +6675,17 @@
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="53" t="inlineStr">
+      <c r="A5" s="59" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="B5" s="54" t="inlineStr">
+      <c r="B5" s="60" t="inlineStr">
         <is>
           <t>NVIDIA</t>
         </is>
       </c>
-      <c r="C5" s="55" t="inlineStr">
+      <c r="C5" s="61" t="inlineStr">
         <is>
           <t>NASDAQ:NVDA</t>
         </is>
@@ -6679,17 +6697,17 @@
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="56" t="inlineStr">
+      <c r="A6" s="62" t="inlineStr">
         <is>
           <t>VIX</t>
         </is>
       </c>
-      <c r="B6" s="57" t="inlineStr">
+      <c r="B6" s="63" t="inlineStr">
         <is>
           <t>CBOE 波動率指數</t>
         </is>
       </c>
-      <c r="C6" s="58" t="inlineStr">
+      <c r="C6" s="64" t="inlineStr">
         <is>
           <t>CBOE:VIX</t>
         </is>
@@ -6701,17 +6719,17 @@
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="53" t="inlineStr">
+      <c r="A7" s="59" t="inlineStr">
         <is>
           <t>XLE</t>
         </is>
       </c>
-      <c r="B7" s="54" t="inlineStr">
+      <c r="B7" s="60" t="inlineStr">
         <is>
           <t>能源類股 ETF</t>
         </is>
       </c>
-      <c r="C7" s="55" t="inlineStr">
+      <c r="C7" s="61" t="inlineStr">
         <is>
           <t>AMEX:XLE</t>
         </is>
@@ -6723,17 +6741,17 @@
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="56" t="inlineStr">
+      <c r="A8" s="62" t="inlineStr">
         <is>
           <t>GOLD</t>
         </is>
       </c>
-      <c r="B8" s="57" t="inlineStr">
+      <c r="B8" s="63" t="inlineStr">
         <is>
           <t>黃金現貨</t>
         </is>
       </c>
-      <c r="C8" s="58" t="inlineStr">
+      <c r="C8" s="64" t="inlineStr">
         <is>
           <t>TVC:GOLD</t>
         </is>
@@ -6745,17 +6763,17 @@
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="53" t="inlineStr">
+      <c r="A9" s="59" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="B9" s="54" t="inlineStr">
+      <c r="B9" s="60" t="inlineStr">
         <is>
           <t>標普 500 指數</t>
         </is>
       </c>
-      <c r="C9" s="55" t="inlineStr">
+      <c r="C9" s="61" t="inlineStr">
         <is>
           <t>SP:SPX</t>
         </is>
@@ -6767,17 +6785,17 @@
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="56" t="inlineStr">
+      <c r="A10" s="62" t="inlineStr">
         <is>
           <t>UKOIL</t>
         </is>
       </c>
-      <c r="B10" s="57" t="inlineStr">
+      <c r="B10" s="63" t="inlineStr">
         <is>
           <t>Brent 原油</t>
         </is>
       </c>
-      <c r="C10" s="58" t="inlineStr">
+      <c r="C10" s="64" t="inlineStr">
         <is>
           <t>TVC:UKOIL</t>
         </is>
@@ -6789,17 +6807,17 @@
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="53" t="inlineStr">
+      <c r="A11" s="59" t="inlineStr">
         <is>
           <t>US10Y</t>
         </is>
       </c>
-      <c r="B11" s="54" t="inlineStr">
+      <c r="B11" s="60" t="inlineStr">
         <is>
           <t>美國 10 年期孳息</t>
         </is>
       </c>
-      <c r="C11" s="55" t="inlineStr">
+      <c r="C11" s="61" t="inlineStr">
         <is>
           <t>TVC:US10Y</t>
         </is>

--- a/output/2026-09-09_四大力量牛熊週期_日內交易框架.xlsx
+++ b/output/2026-09-09_四大力量牛熊週期_日內交易框架.xlsx
@@ -218,7 +218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -357,6 +357,60 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -6675,17 +6729,17 @@
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="59" t="inlineStr">
+      <c r="A5" s="77" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="B5" s="60" t="inlineStr">
+      <c r="B5" s="78" t="inlineStr">
         <is>
           <t>NVIDIA</t>
         </is>
       </c>
-      <c r="C5" s="61" t="inlineStr">
+      <c r="C5" s="79" t="inlineStr">
         <is>
           <t>NASDAQ:NVDA</t>
         </is>
@@ -6697,17 +6751,17 @@
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="62" t="inlineStr">
+      <c r="A6" s="80" t="inlineStr">
         <is>
           <t>VIX</t>
         </is>
       </c>
-      <c r="B6" s="63" t="inlineStr">
+      <c r="B6" s="81" t="inlineStr">
         <is>
           <t>CBOE 波動率指數</t>
         </is>
       </c>
-      <c r="C6" s="64" t="inlineStr">
+      <c r="C6" s="82" t="inlineStr">
         <is>
           <t>CBOE:VIX</t>
         </is>
@@ -6719,17 +6773,17 @@
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="59" t="inlineStr">
+      <c r="A7" s="77" t="inlineStr">
         <is>
           <t>XLE</t>
         </is>
       </c>
-      <c r="B7" s="60" t="inlineStr">
+      <c r="B7" s="78" t="inlineStr">
         <is>
           <t>能源類股 ETF</t>
         </is>
       </c>
-      <c r="C7" s="61" t="inlineStr">
+      <c r="C7" s="79" t="inlineStr">
         <is>
           <t>AMEX:XLE</t>
         </is>
@@ -6741,17 +6795,17 @@
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="62" t="inlineStr">
+      <c r="A8" s="80" t="inlineStr">
         <is>
           <t>GOLD</t>
         </is>
       </c>
-      <c r="B8" s="63" t="inlineStr">
+      <c r="B8" s="81" t="inlineStr">
         <is>
           <t>黃金現貨</t>
         </is>
       </c>
-      <c r="C8" s="64" t="inlineStr">
+      <c r="C8" s="82" t="inlineStr">
         <is>
           <t>TVC:GOLD</t>
         </is>
@@ -6763,17 +6817,17 @@
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="59" t="inlineStr">
+      <c r="A9" s="77" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="B9" s="60" t="inlineStr">
+      <c r="B9" s="78" t="inlineStr">
         <is>
           <t>標普 500 指數</t>
         </is>
       </c>
-      <c r="C9" s="61" t="inlineStr">
+      <c r="C9" s="79" t="inlineStr">
         <is>
           <t>SP:SPX</t>
         </is>
@@ -6785,17 +6839,17 @@
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="62" t="inlineStr">
+      <c r="A10" s="80" t="inlineStr">
         <is>
           <t>UKOIL</t>
         </is>
       </c>
-      <c r="B10" s="63" t="inlineStr">
+      <c r="B10" s="81" t="inlineStr">
         <is>
           <t>Brent 原油</t>
         </is>
       </c>
-      <c r="C10" s="64" t="inlineStr">
+      <c r="C10" s="82" t="inlineStr">
         <is>
           <t>TVC:UKOIL</t>
         </is>
@@ -6807,17 +6861,17 @@
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="59" t="inlineStr">
+      <c r="A11" s="77" t="inlineStr">
         <is>
           <t>US10Y</t>
         </is>
       </c>
-      <c r="B11" s="60" t="inlineStr">
+      <c r="B11" s="78" t="inlineStr">
         <is>
           <t>美國 10 年期孳息</t>
         </is>
       </c>
-      <c r="C11" s="61" t="inlineStr">
+      <c r="C11" s="79" t="inlineStr">
         <is>
           <t>TVC:US10Y</t>
         </is>
